--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104550_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104550_W11.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4378</v>
+        <v>4.3459</v>
       </c>
       <c r="E2" t="n">
-        <v>3.6569</v>
+        <v>3.4288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7809</v>
+        <v>0.9171</v>
       </c>
       <c r="G2" t="n">
-        <v>2.957</v>
+        <v>2.9499</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0334</v>
+        <v>3.0328</v>
       </c>
       <c r="J2" t="n">
-        <v>3.0792</v>
+        <v>3.0642</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6163</v>
+        <v>0.6065</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4629</v>
+        <v>2.4576</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1222</v>
+        <v>-0.1143</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5734</v>
+        <v>0.4855</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5777</v>
+        <v>0.3646</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0042</v>
+        <v>0.1209</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5796</v>
+        <v>1.7783</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5585</v>
+        <v>1.0382</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0211</v>
+        <v>0.7401</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5577</v>
+        <v>2.5647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5612</v>
+        <v>0.5656</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9965</v>
+        <v>1.9992</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1085</v>
+        <v>3.0931</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5066</v>
+        <v>1.4996</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5507</v>
+        <v>-0.5284</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9538</v>
+        <v>1.1452</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1039</v>
+        <v>0.6083</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8498</v>
+        <v>0.5369</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0605</v>
+        <v>1.4976</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8047</v>
+        <v>0.303</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7441</v>
+        <v>1.1946</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3084</v>
+        <v>-1.231</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0563</v>
+        <v>0.948</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3647</v>
+        <v>-2.179</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5618</v>
+        <v>-0.2028</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8285</v>
+        <v>2.0544</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2666</v>
+        <v>-2.2572</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8702</v>
+        <v>-1.0282</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7721</v>
+        <v>-1.1064</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0981</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>1.8211</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0079</v>
+        <v>1.0766</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1916</v>
+        <v>0.5757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8163</v>
+        <v>0.501</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5463</v>
+        <v>-0.1691</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1853</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.7317</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.305</v>
+        <v>1.4805</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8787</v>
+        <v>3.0022</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5737</v>
+        <v>-1.5218</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5888</v>
+        <v>1.5959</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4213</v>
+        <v>0.4249</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1675</v>
+        <v>1.171</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5478</v>
+        <v>2.5403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8312</v>
+        <v>0.8274</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7166</v>
+        <v>1.7129</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.959</v>
+        <v>-0.9444</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7292</v>
+        <v>-0.5609</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6956</v>
+        <v>-0.5576</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0336</v>
+        <v>-0.0033</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2185</v>
+        <v>0.2179</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0349</v>
+        <v>-1.0293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.074</v>
+        <v>1.378</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1153</v>
+        <v>3.6785</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1892</v>
+        <v>-2.3005</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2333</v>
+        <v>-0.3084</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9524</v>
+        <v>1.0514</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.1857</v>
+        <v>-1.3598</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1762</v>
+        <v>1.5371</v>
       </c>
       <c r="K6" t="n">
-        <v>2.0709</v>
+        <v>1.8131</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.2471</v>
+        <v>-0.276</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.057</v>
+        <v>-1.8455</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1185</v>
+        <v>-0.7617</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0614</v>
+        <v>-1.0838</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8147</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2268</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6596</v>
+        <v>1.3206</v>
       </c>
       <c r="T6" t="n">
-        <v>0.127</v>
+        <v>1.1006</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5326</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1671</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>2.1789</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3278</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4922</v>
+        <v>0.0023</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0502</v>
+        <v>1.1847</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4419</v>
+        <v>-1.1825</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5886</v>
+        <v>1.5888</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9624</v>
+        <v>-0.9676</v>
       </c>
       <c r="I7" t="n">
-        <v>2.551</v>
+        <v>2.5564</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5711</v>
+        <v>2.5461</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2975</v>
+        <v>0.2823</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9825</v>
+        <v>-0.9573</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2773</v>
+        <v>0.2926</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3076</v>
+        <v>1.1858</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3115</v>
+        <v>0.9637</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0039</v>
+        <v>0.2221</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>M. JIMENEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6366</v>
+        <v>-1.8017</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7237</v>
+        <v>-0.1304</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0871</v>
+        <v>-1.6714</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5394</v>
+        <v>-1.2013</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1472</v>
+        <v>0.4654</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6078</v>
+        <v>-1.6667</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7317</v>
+        <v>0.1299</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.769</v>
+        <v>0.8823</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0373</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1923</v>
+        <v>-1.3312</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3781</v>
+        <v>-0.4169</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5705</v>
+        <v>-0.9143</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3648</v>
+        <v>-0.4215</v>
       </c>
       <c r="T8" t="n">
-        <v>0.369</v>
+        <v>-0.2603</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0042</v>
+        <v>-0.1612</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.3278</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.3278</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. JIMENEZ</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0487</v>
+        <v>-1.9104</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3245</v>
+        <v>-2.1336</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7242</v>
+        <v>0.2233</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2037</v>
+        <v>-0.5336</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4676</v>
+        <v>-1.146</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6712</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1443</v>
+        <v>-0.7352</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8934</v>
+        <v>-0.7724</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.749</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.348</v>
+        <v>0.2016</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4258</v>
+        <v>-0.3736</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9222</v>
+        <v>0.5752</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6596</v>
+        <v>0.0882</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4688</v>
+        <v>-0.0327</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1909</v>
+        <v>0.1209</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-0.3268</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>C. AGADA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1157</v>
+        <v>-2.8725</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1599</v>
+        <v>-2.1134</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9558</v>
+        <v>-0.7591</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9193</v>
+        <v>-2.0355</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5888</v>
+        <v>-0.6052</v>
       </c>
       <c r="I10" t="n">
-        <v>0.3306</v>
+        <v>-1.4303</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1829</v>
+        <v>-0.6622</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1083</v>
+        <v>0.1132</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0746</v>
+        <v>-0.7754</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2636</v>
+        <v>-1.3733</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5195</v>
+        <v>-0.7184</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2559</v>
+        <v>-0.6549</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0765</v>
+        <v>0.223</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>0.1925</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1322</v>
+        <v>0.0305</v>
       </c>
       <c r="V10" t="n">
-        <v>-3.278</v>
+        <v>0.5334</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X10" t="n">
-        <v>-3.278</v>
+        <v>-0.3268</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>C. AGADA</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5052</v>
+        <v>-2.8746</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7883</v>
+        <v>-0.0302</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7169</v>
+        <v>-2.8444</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0134</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5899</v>
+        <v>0.5861</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4234</v>
+        <v>0.3338</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6226</v>
+        <v>1.1776</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1345</v>
+        <v>1.1032</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7572</v>
+        <v>0.0745</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3908</v>
+        <v>-0.2578</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7245</v>
+        <v>-0.5171</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6663</v>
+        <v>0.2593</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.444</v>
+        <v>0.1568</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5383</v>
+        <v>-0.0697</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0944</v>
+        <v>0.2265</v>
       </c>
       <c r="V11" t="n">
-        <v>0.54</v>
+        <v>-3.2684</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8678</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8911</v>
+        <v>-3.5021</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8523</v>
+        <v>-2.8714</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0388</v>
+        <v>-0.6307</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9295</v>
+        <v>-2.9343</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.4471</v>
+        <v>-2.4579</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4824</v>
+        <v>-0.4764</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5738</v>
+        <v>-1.6047</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3445</v>
+        <v>-1.3659</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2293</v>
+        <v>-0.2388</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3557</v>
+        <v>-1.3296</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2531</v>
+        <v>-0.2377</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4984</v>
+        <v>0.8988</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8953</v>
+        <v>0.9217</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3968</v>
+        <v>-0.0229</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5527</v>
+        <v>-0.5561</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8741</v>
+        <v>-0.8716</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.232600000000001</v>
+        <v>-2.478700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>3.884599999999998</v>
+        <v>5.356399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.117099999999999</v>
+        <v>-7.835299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.383699999999999</v>
+        <v>1.3751</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.1754</v>
+        <v>-1.2182</v>
       </c>
       <c r="I13" t="n">
-        <v>2.559399999999999</v>
+        <v>2.5934</v>
       </c>
       <c r="J13" t="n">
-        <v>11.0913</v>
+        <v>10.8834</v>
       </c>
       <c r="K13" t="n">
-        <v>7.1737</v>
+        <v>7.043699999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.9177</v>
+        <v>3.839699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.707400000000002</v>
+        <v>-9.508399999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.3489</v>
+        <v>-8.262</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.3585</v>
+        <v>-1.2464</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.1343</v>
+        <v>-1.1383</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7442</v>
+        <v>-14.796</v>
       </c>
       <c r="R13" t="n">
-        <v>13.6099</v>
+        <v>13.6579</v>
       </c>
       <c r="S13" t="n">
-        <v>3.841</v>
+        <v>5.598099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>2.0416</v>
+        <v>3.8068</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7995</v>
+        <v>1.7914</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.323400000000001</v>
+        <v>-8.3139</v>
       </c>
       <c r="W13" t="n">
-        <v>5.495699999999999</v>
+        <v>5.462199999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-13.8192</v>
+        <v>-13.7761</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.234</v>
+        <v>4.4136</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5584</v>
+        <v>4.3052</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3245</v>
+        <v>0.1084</v>
       </c>
       <c r="G14" t="n">
-        <v>5.0233</v>
+        <v>5.0209</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7531</v>
+        <v>0.758</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2701</v>
+        <v>4.263</v>
       </c>
       <c r="J14" t="n">
-        <v>4.7641</v>
+        <v>4.7468</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8485</v>
+        <v>0.8446</v>
       </c>
       <c r="L14" t="n">
-        <v>3.9156</v>
+        <v>3.9022</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2592</v>
+        <v>0.2741</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3018</v>
+        <v>-0.1301</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0212</v>
+        <v>-0.214</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.323</v>
+        <v>0.0838</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.3948</v>
+        <v>-1.3877</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.3948</v>
+        <v>-1.3877</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3047</v>
+        <v>4.2881</v>
       </c>
       <c r="E15" t="n">
-        <v>5.6172</v>
+        <v>6.1564</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3125</v>
+        <v>-1.8684</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0987</v>
+        <v>-0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8369</v>
+        <v>0.8386</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9356</v>
+        <v>-0.9386</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1228</v>
+        <v>2.0914</v>
       </c>
       <c r="K15" t="n">
-        <v>2.019</v>
+        <v>2.0027</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1038</v>
+        <v>0.0887</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.2215</v>
+        <v>-2.1915</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8745</v>
+        <v>-0.8803</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8347</v>
+        <v>-0.2442</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0398</v>
+        <v>-0.6361</v>
       </c>
       <c r="V15" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="W15" t="n">
-        <v>5.4633</v>
+        <v>5.4474</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9426</v>
+        <v>3.2716</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1712</v>
+        <v>2.2509</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7714</v>
+        <v>1.0208</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6444</v>
+        <v>-1.644</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0664</v>
+        <v>-0.0634</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.578</v>
+        <v>-1.5806</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5501</v>
+        <v>-0.5679999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4608</v>
+        <v>-1.4676</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0944</v>
+        <v>-1.0759</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9352</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8347</v>
+        <v>-0.718</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1004</v>
+        <v>0.1187</v>
       </c>
       <c r="V16" t="n">
-        <v>4.6149</v>
+        <v>4.6044</v>
       </c>
       <c r="W16" t="n">
-        <v>4.917</v>
+        <v>4.9026</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3021</v>
+        <v>-0.2983</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2844</v>
+        <v>1.7535</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6136</v>
+        <v>3.0627</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3292</v>
+        <v>-1.3092</v>
       </c>
       <c r="G17" t="n">
-        <v>2.228</v>
+        <v>2.2273</v>
       </c>
       <c r="H17" t="n">
-        <v>1.5483</v>
+        <v>1.5481</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6797</v>
+        <v>0.6792</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0955</v>
+        <v>4.0756</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4936</v>
+        <v>2.4821</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6019</v>
+        <v>1.5935</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8675</v>
+        <v>-1.8483</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9453</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9222</v>
+        <v>-0.9143</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.49</v>
+        <v>-0.0185</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3478</v>
+        <v>0.1253</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1422</v>
+        <v>-0.1438</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5964</v>
+        <v>1.4234</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5915</v>
+        <v>1.4401</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005</v>
+        <v>-0.0167</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7328</v>
+        <v>0.1468</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5382</v>
+        <v>1.3524</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1946</v>
+        <v>-1.2056</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5915</v>
+        <v>1.6632</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5541</v>
+        <v>1.9995</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>-0.3362</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1414</v>
+        <v>-1.5164</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0159</v>
+        <v>-0.6471</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>-0.8694</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1364</v>
+        <v>-0.4471</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.1258</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1364</v>
+        <v>-0.3213</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3221</v>
+        <v>0.7451</v>
       </c>
       <c r="E19" t="n">
-        <v>0.779</v>
+        <v>0.7073</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4569</v>
+        <v>0.0378</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1519</v>
+        <v>0.7323</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3462</v>
+        <v>0.5371</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1942</v>
+        <v>0.1952</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6967</v>
+        <v>0.5888</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0087</v>
+        <v>0.5516</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3121</v>
+        <v>0.0372</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5447</v>
+        <v>0.1435</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6626</v>
+        <v>-0.0144</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8822</v>
+        <v>0.1579</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5615</v>
+        <v>0.0128</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8347</v>
+        <v>0.1184</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7268</v>
+        <v>-0.1057</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. TAVARES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.058</v>
+        <v>-1.4093</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6321</v>
+        <v>-1.7742</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5742</v>
+        <v>0.3649</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4193</v>
+        <v>-2.2072</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4993</v>
+        <v>-0.8334</v>
       </c>
       <c r="I20" t="n">
-        <v>0.08</v>
+        <v>-1.3738</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8778</v>
+        <v>-1.0167</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1314</v>
+        <v>0.0862</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7463</v>
+        <v>-1.1029</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2971</v>
+        <v>-1.1906</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6308</v>
+        <v>-0.9196</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6663</v>
+        <v>-0.271</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-0.2276</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6775</v>
+        <v>-0.0419</v>
       </c>
       <c r="T20" t="n">
-        <v>2.4498</v>
+        <v>-0.5298</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2277</v>
+        <v>0.4879</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3856</v>
+        <v>-0.2983</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-0.2983</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7411</v>
+        <v>-1.4551</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0996</v>
+        <v>-1.8743</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3585</v>
+        <v>0.4192</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.036</v>
+        <v>-1.0258</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4705</v>
+        <v>-1.4623</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4345</v>
+        <v>0.4365</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0266</v>
+        <v>0.0213</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6825</v>
+        <v>-0.6862</v>
       </c>
       <c r="L21" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0626</v>
+        <v>-1.0471</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.788</v>
+        <v>-0.7761</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2745</v>
+        <v>-0.271</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2423</v>
+        <v>0.0267</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7652</v>
+        <v>-0.5298</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5229</v>
+        <v>0.5565</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.4628</v>
+        <v>-0.456</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.4628</v>
+        <v>-0.456</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>E. TAVARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8111</v>
+        <v>-2.228</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9957</v>
+        <v>-1.2769</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1846</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2077</v>
+        <v>-0.4045</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.8428</v>
+        <v>-0.4943</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.3648</v>
+        <v>0.0898</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.0037</v>
+        <v>0.8686</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0866</v>
+        <v>0.1239</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0903</v>
+        <v>0.7447</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2039</v>
+        <v>-1.2731</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9294</v>
+        <v>-0.6182</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2745</v>
+        <v>-0.6549</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1342</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2268</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4355</v>
+        <v>0.3845</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7652</v>
+        <v>0.5664</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3297</v>
+        <v>-0.1819</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3021</v>
+        <v>-0.387</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.3021</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3171</v>
+        <v>-2.4689</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6796</v>
+        <v>-2.9515</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3625</v>
+        <v>0.4826</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.6768</v>
+        <v>-1.6897</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5572</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2338</v>
+        <v>-2.2469</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.747</v>
+        <v>-1.7771</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8414</v>
+        <v>0.8306</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5884</v>
+        <v>-2.6077</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0701</v>
+        <v>0.0873</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O23" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1113</v>
+        <v>-0.2532</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0066</v>
+        <v>0.1002</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3021</v>
+        <v>-0.2983</v>
       </c>
       <c r="W23" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8485</v>
+        <v>-0.843</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6401</v>
+        <v>-2.5334</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.071</v>
+        <v>-2.2104</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5692</v>
+        <v>-0.323</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4369</v>
+        <v>-2.4313</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.5253</v>
+        <v>-1.5196</v>
       </c>
       <c r="I24" t="n">
         <v>-0.9116</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.1667</v>
+        <v>-1.1858</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8627</v>
+        <v>-0.8726</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.2702</v>
+        <v>-1.2455</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4301</v>
+        <v>-0.3297</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6599</v>
+        <v>-0.4433</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.232800000000001</v>
+        <v>5.800599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>8.117100000000001</v>
+        <v>7.835300000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8845</v>
+        <v>-2.0347</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.383799999999999</v>
+        <v>-1.375199999999998</v>
       </c>
       <c r="H25" t="n">
-        <v>1.1754</v>
+        <v>1.2184</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.5591</v>
+        <v>-2.5934</v>
       </c>
       <c r="J25" t="n">
-        <v>9.7075</v>
+        <v>9.508099999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>8.348800000000001</v>
+        <v>8.262</v>
       </c>
       <c r="L25" t="n">
-        <v>1.358399999999999</v>
+        <v>1.2462</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.0912</v>
+        <v>-10.8835</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.1736</v>
+        <v>-7.043599999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.917600000000001</v>
+        <v>-3.8398</v>
       </c>
       <c r="P25" t="n">
-        <v>1.134000000000001</v>
+        <v>1.138</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.61</v>
+        <v>-13.658</v>
       </c>
       <c r="R25" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S25" t="n">
-        <v>-3.8411</v>
+        <v>-2.2761</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.7993</v>
+        <v>-1.7913</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.0416</v>
+        <v>-0.4850000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>8.323500000000001</v>
+        <v>8.3139</v>
       </c>
       <c r="W25" t="n">
-        <v>13.819</v>
+        <v>13.7761</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.495699999999999</v>
+        <v>-5.4623</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104550_W11.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104550_W11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0293</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3268</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.8716</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-13.7761</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.3877</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.2983</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.2983</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.456</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.843</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104550_W11.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-5.4623</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
